--- a/data/trans_orig/IP07_C15_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP07_C15_2023-Clase-trans_orig.xlsx
@@ -535,13 +535,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si se han producido situaciones de cyberbulling fuera de su colegio en 2023 (tasa de respuesta: 92,89%)</t>
+          <t>Menores según si se han producido situaciones de cyberbulling fuera de su colegio/instituto en 2023 (tasa de respuesta: 92,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1629</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>498</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>4274</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>4,89%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>1,5%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>12,84%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>3866</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1387</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>8099</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>13,57%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>4,87%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>28,42%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1929</t>
+          <t>4010</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>539</t>
+          <t>1475</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4823</t>
+          <t>8006</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>26,85%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>5795</t>
+          <t>5639</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3015</t>
+          <t>3104</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10256</t>
+          <t>10750</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>17,04%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>31652</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>29007</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>32783</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>95,11%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>87,16%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>98,5%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>24630</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>20397</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>27109</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>86,43%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>71,58%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>95,13%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>30428</t>
+          <t>25807</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>27534</t>
+          <t>21811</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>31818</t>
+          <t>28342</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>94,04%</t>
+          <t>86,55%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>85,09%</t>
+          <t>73,15%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>95,05%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>55058</t>
+          <t>57459</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>50597</t>
+          <t>52348</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>57838</t>
+          <t>59994</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>90,48%</t>
+          <t>91,06%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>83,15%</t>
+          <t>82,96%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,05%</t>
+          <t>95,08%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>33281</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>33281</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>33281</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>28496</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>28496</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>28496</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>32357</t>
+          <t>29817</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>32357</t>
+          <t>29817</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>32357</t>
+          <t>29817</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>60853</t>
+          <t>63098</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>60853</t>
+          <t>63098</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>60853</t>
+          <t>63098</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>3443</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>894</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>7507</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>11,2%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>2,91%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>24,42%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>1729</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>1832</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>5960</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>6,18%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>6383</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>6,19%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>21,31%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>3510</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>7737</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>11,71%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>3,15%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>25,81%</t>
+          <t>21,58%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>5239</t>
+          <t>5275</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1877</t>
+          <t>2080</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>10068</t>
+          <t>11258</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>18,67%</t>
         </is>
       </c>
     </row>
@@ -1176,74 +1176,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>27293</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>23229</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>29842</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>88,8%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>75,58%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>97,09%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>26234</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>22003</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>27963</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>93,82%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>78,69%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>27745</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>23194</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>29577</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>93,81%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>78,42%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>26471</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>22244</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>29036</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>88,29%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>74,19%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>96,85%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>72</t>
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>52706</t>
+          <t>55038</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>47877</t>
+          <t>49055</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>56068</t>
+          <t>58233</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>90,96%</t>
+          <t>91,25%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>82,62%</t>
+          <t>81,33%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>96,55%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>27963</t>
+          <t>30736</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>27963</t>
+          <t>30736</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>27963</t>
+          <t>30736</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>29981</t>
+          <t>29577</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>29981</t>
+          <t>29577</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>29981</t>
+          <t>29577</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>57945</t>
+          <t>60313</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>57945</t>
+          <t>60313</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>57945</t>
+          <t>60313</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,7 +1411,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1397</t>
+          <t>1223</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1421,12 +1421,12 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4513</t>
+          <t>4055</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>32,98%</t>
+          <t>15,39%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,7 +1446,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>1314</t>
+          <t>1444</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -1456,12 +1456,12 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4525</t>
+          <t>4437</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>29,95%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>2711</t>
+          <t>2666</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>801</t>
+          <t>662</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6754</t>
+          <t>6953</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>16,89%</t>
         </is>
       </c>
     </row>
@@ -1519,74 +1519,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>25127</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>22295</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>26350</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>95,36%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>84,61%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>12287</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>9171</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>13684</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>89,79%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>67,02%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>13372</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>10379</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>14816</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>90,26%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>70,05%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>25692</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>22481</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>27006</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>95,13%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>83,24%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>47</t>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>37979</t>
+          <t>38500</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>33936</t>
+          <t>34213</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>39889</t>
+          <t>40504</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>93,34%</t>
+          <t>93,52%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>83,4%</t>
+          <t>83,11%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>98,39%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>26350</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>26350</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>26350</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>13684</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>13684</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>13684</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>27006</t>
+          <t>14816</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>27006</t>
+          <t>14816</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>27006</t>
+          <t>14816</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>40690</t>
+          <t>41166</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>40690</t>
+          <t>41166</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>40690</t>
+          <t>41166</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>7226</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>3140</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>14063</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>11,58%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>5,03%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>22,54%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>7740</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>1647</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>16798</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>11,98%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>2,55%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>26,0%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>7642</t>
+          <t>7743</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3714</t>
+          <t>4242</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>15342</t>
+          <t>13462</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>18,9%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,97%</t>
+          <t>32,86%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>15382</t>
+          <t>14969</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>7583</t>
+          <t>9589</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>25410</t>
+          <t>24049</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>23,27%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>55175</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>48338</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>59261</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>88,42%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>77,46%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>94,97%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>56865</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>47807</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>62958</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>88,02%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>74,0%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>97,45%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>56353</t>
+          <t>33222</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>48653</t>
+          <t>27503</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>60281</t>
+          <t>36723</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>88,06%</t>
+          <t>81,1%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>76,03%</t>
+          <t>67,14%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,2%</t>
+          <t>89,64%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>113217</t>
+          <t>88397</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>103189</t>
+          <t>79317</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>121016</t>
+          <t>93777</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>88,04%</t>
+          <t>85,52%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>80,24%</t>
+          <t>76,73%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>90,72%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>62401</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>62401</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>62401</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>57</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>64605</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>64605</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>64605</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>63995</t>
+          <t>40965</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>63995</t>
+          <t>40965</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>63995</t>
+          <t>40965</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>128599</t>
+          <t>103366</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>128599</t>
+          <t>103366</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>128599</t>
+          <t>103366</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,32 +2097,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>3053</t>
+          <t>5428</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1219</t>
+          <t>1872</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6721</t>
+          <t>11279</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>19,88%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>5851</t>
+          <t>3317</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1946</t>
+          <t>1271</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>13054</t>
+          <t>6511</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>22,35%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>8904</t>
+          <t>8745</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4372</t>
+          <t>4262</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>16061</t>
+          <t>15549</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>16,73%</t>
         </is>
       </c>
     </row>
@@ -2205,72 +2205,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>51306</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>45455</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>54862</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>90,43%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>80,12%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>96,7%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>30042</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>26374</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>31876</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>90,78%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>79,69%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>96,32%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>52569</t>
+          <t>32884</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>45366</t>
+          <t>29690</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>56474</t>
+          <t>34930</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>89,98%</t>
+          <t>90,84%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>77,65%</t>
+          <t>82,01%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>96,49%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>82610</t>
+          <t>84189</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>75453</t>
+          <t>77385</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>87142</t>
+          <t>88672</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>90,27%</t>
+          <t>90,59%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>82,45%</t>
+          <t>83,27%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>95,41%</t>
         </is>
       </c>
     </row>
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>56734</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>56734</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>56734</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>50</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>33095</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>33095</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>33095</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>58420</t>
+          <t>36201</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>58420</t>
+          <t>36201</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>58420</t>
+          <t>36201</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>91514</t>
+          <t>92934</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>91514</t>
+          <t>92934</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>91514</t>
+          <t>92934</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2435,72 +2435,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>4902</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>9125</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>14,46%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>5,9%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>26,91%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>2737</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>859</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>6926</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>9,87%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>3,1%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>24,98%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>5202</t>
+          <t>2832</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2352</t>
+          <t>654</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>9775</t>
+          <t>7693</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>29,3%</t>
+          <t>25,2%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>7939</t>
+          <t>7735</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4218</t>
+          <t>3835</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>13318</t>
+          <t>13127</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>21,8%</t>
+          <t>20,37%</t>
         </is>
       </c>
     </row>
@@ -2548,72 +2548,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>29002</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>24779</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>31904</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>85,54%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>73,09%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>94,1%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>24988</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>20799</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>26866</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>90,13%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>75,02%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>96,9%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>28157</t>
+          <t>27695</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>23584</t>
+          <t>22834</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>31007</t>
+          <t>29873</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>84,41%</t>
+          <t>90,72%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>70,7%</t>
+          <t>74,8%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>92,95%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>53146</t>
+          <t>56696</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>47767</t>
+          <t>51304</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>56867</t>
+          <t>60596</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>87,0%</t>
+          <t>88,0%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>78,2%</t>
+          <t>79,63%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>93,09%</t>
+          <t>94,05%</t>
         </is>
       </c>
     </row>
@@ -2661,57 +2661,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>33904</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>33904</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>33904</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>39</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>27725</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>27725</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>27725</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>33359</t>
+          <t>30527</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>33359</t>
+          <t>30527</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>33359</t>
+          <t>30527</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>61085</t>
+          <t>64431</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>61085</t>
+          <t>64431</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>61085</t>
+          <t>64431</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2783,32 +2783,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>20521</t>
+          <t>23851</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>11421</t>
+          <t>16099</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>28701</t>
+          <t>34093</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>14,01%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,32 +2818,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>25449</t>
+          <t>21178</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>16951</t>
+          <t>14658</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>35816</t>
+          <t>29232</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>16,07%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>45970</t>
+          <t>45029</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>33458</t>
+          <t>33956</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>60263</t>
+          <t>57774</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>13,58%</t>
         </is>
       </c>
     </row>
@@ -2891,72 +2891,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>248</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>219555</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>209313</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>227307</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>90,2%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>85,99%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>93,39%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>216</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>175048</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>166868</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>184148</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>89,51%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>85,32%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>94,16%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>248</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>219669</t>
+          <t>160724</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>209302</t>
+          <t>152670</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>228167</t>
+          <t>167244</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>89,62%</t>
+          <t>88,36%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>85,39%</t>
+          <t>83,93%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>93,08%</t>
+          <t>91,94%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>394717</t>
+          <t>380279</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>380424</t>
+          <t>367534</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>407229</t>
+          <t>391352</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>89,57%</t>
+          <t>89,41%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>86,33%</t>
+          <t>86,42%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>92,41%</t>
+          <t>92,02%</t>
         </is>
       </c>
     </row>
@@ -3004,57 +3004,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>279</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>243406</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>243406</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>243406</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>247</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>195569</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>195569</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>195569</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>279</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>245118</t>
+          <t>181902</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>245118</t>
+          <t>181902</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>245118</t>
+          <t>181902</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>440687</t>
+          <t>425308</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>440687</t>
+          <t>425308</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>440687</t>
+          <t>425308</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
